--- a/Data/EXCEL/Transfer/salemon/20240711/6497-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6497-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{535EBFFE-35F9-4E46-8B14-30254D611E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ABC06C7-4ADD-4D19-912B-3039390E80C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{E11809E9-9008-44E2-A0B2-A1293B3ECFF6}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{20896F0B-2699-4768-AE01-CCF14EEAB874}"/>
   </bookViews>
   <sheets>
     <sheet name="6497-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1247,23 +1247,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{170EBE4B-10FE-481C-A19C-535E2D78CEAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDB0D10-FCBD-4A6F-A497-330185F5DB2B}">
   <dimension ref="A1:Q91"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="P1" s="17"/>
       <c r="Q1" s="18"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="13" t="s">
         <v>4</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Q2" s="18"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
@@ -1372,7 +1372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -1411,7 +1411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>44044</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>44013</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>43983</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>43952</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>43922</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>43891</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>43862</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>43831</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>43800</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>43770</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>43739</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>43709</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>43678</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>43647</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>43617</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>43586</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>43556</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>43525</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>43497</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>43466</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>43435</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>43405</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>43374</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>43344</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>43313</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>43282</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>43252</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>43221</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>43191</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>43160</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>43132</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>43101</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>43070</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>43040</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>43009</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>42979</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>42948</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>42917</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>42887</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>42856</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>42826</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>42795</v>
       </c>
@@ -3637,227 +3637,227 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>42795</v>
       </c>
